--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E7B9A38-B9D0-4478-A34E-0A4EE32E7AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{480CA6CA-2A4A-4F51-884F-CAD8BFA3B9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{4BF46AEC-753C-47EA-A26B-119EC5635F4C}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{A93CECFF-1D1D-45EF-8921-D092737CFBE7}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6D00D3-631B-405D-9CDC-B3EF893F9F88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D3DBCD9-D3B8-4223-9479-D51EAD6AA8E8}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4512CF02-0892-4F57-B50F-400FE479C8D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537491C9-3CBB-4803-8072-049DF9F218C6}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11470,7 +11470,7 @@
         <v>14</v>
       </c>
       <c r="R108" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S108" t="s">
         <v>500</v>
@@ -11532,7 +11532,7 @@
         <v>14</v>
       </c>
       <c r="R109" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S109" t="s">
         <v>500</v>
@@ -12338,7 +12338,7 @@
         <v>14</v>
       </c>
       <c r="R122" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S122" t="s">
         <v>500</v>
@@ -12400,7 +12400,7 @@
         <v>14</v>
       </c>
       <c r="R123" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S123" t="s">
         <v>500</v>
@@ -12586,7 +12586,7 @@
         <v>14</v>
       </c>
       <c r="R126" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S126" t="s">
         <v>500</v>
@@ -12648,7 +12648,7 @@
         <v>14</v>
       </c>
       <c r="R127" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S127" t="s">
         <v>500</v>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E50B63-1396-4427-892F-45B90D9E1AB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088079FE-DA4F-4BED-B2BE-DAF12E556C7F}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC149904-7DBF-4CF4-BE7B-764BFC31F882}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9AF7E6-B4A6-4E64-ADFA-597F5A6ED0E2}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35401,7 +35401,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S114" t="s">
         <v>500</v>
@@ -35460,7 +35460,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S115" t="s">
         <v>500</v>
@@ -38029,10 +38029,10 @@
         <v>2024</v>
       </c>
       <c r="G159">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="H159">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="I159">
         <v>1610</v>
@@ -38088,10 +38088,10 @@
         <v>2024</v>
       </c>
       <c r="G160">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H160">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I160">
         <v>1610</v>
@@ -38976,16 +38976,16 @@
         <v>0.1</v>
       </c>
       <c r="H175">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I175">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="J175">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="K175">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L175">
         <v>50</v>
@@ -39035,16 +39035,16 @@
         <v>0.1</v>
       </c>
       <c r="H176">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="I176">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="J176">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="K176">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="L176">
         <v>50</v>
@@ -51168,7 +51168,7 @@
         <v>14</v>
       </c>
       <c r="R382" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S382" t="s">
         <v>500</v>
@@ -51227,7 +51227,7 @@
         <v>14</v>
       </c>
       <c r="R383" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S383" t="s">
         <v>500</v>
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F06408F-2870-4832-A22A-A26E8B65709E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B0FF71-450F-4164-841D-1C53E6C88954}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{480CA6CA-2A4A-4F51-884F-CAD8BFA3B9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4DA6B0E-9CEA-4C0C-B5A3-D0065D32E049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{A93CECFF-1D1D-45EF-8921-D092737CFBE7}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{1A497B3C-2D05-41F7-91CE-D66BB5CD0832}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D3DBCD9-D3B8-4223-9479-D51EAD6AA8E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B51791-16B5-4842-AAE2-6863B68BD284}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{537491C9-3CBB-4803-8072-049DF9F218C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5651E21-F22A-4A71-B603-C8F5842A0D36}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11470,7 +11470,7 @@
         <v>14</v>
       </c>
       <c r="R108" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S108" t="s">
         <v>500</v>
@@ -11532,7 +11532,7 @@
         <v>14</v>
       </c>
       <c r="R109" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S109" t="s">
         <v>500</v>
@@ -12710,7 +12710,7 @@
         <v>14</v>
       </c>
       <c r="R128" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S128" t="s">
         <v>500</v>
@@ -12772,7 +12772,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S129" t="s">
         <v>500</v>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{088079FE-DA4F-4BED-B2BE-DAF12E556C7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C057A573-EB7B-4D36-870A-949B51E5E205}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E9AF7E6-B4A6-4E64-ADFA-597F5A6ED0E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE4FF06-0E54-4F26-8608-8D83DBEB9C30}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35401,7 +35401,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S114" t="s">
         <v>500</v>
@@ -35460,7 +35460,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S115" t="s">
         <v>500</v>
@@ -36463,7 +36463,7 @@
         <v>14</v>
       </c>
       <c r="R132" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S132" t="s">
         <v>500</v>
@@ -36522,7 +36522,7 @@
         <v>14</v>
       </c>
       <c r="R133" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S133" t="s">
         <v>500</v>
@@ -36581,7 +36581,7 @@
         <v>14</v>
       </c>
       <c r="R134" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S134" t="s">
         <v>500</v>
@@ -36640,7 +36640,7 @@
         <v>14</v>
       </c>
       <c r="R135" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S135" t="s">
         <v>500</v>
@@ -51168,7 +51168,7 @@
         <v>14</v>
       </c>
       <c r="R382" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S382" t="s">
         <v>500</v>
@@ -51227,7 +51227,7 @@
         <v>14</v>
       </c>
       <c r="R383" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S383" t="s">
         <v>500</v>
@@ -52967,7 +52967,7 @@
         <v>33</v>
       </c>
       <c r="M431">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016432</v>
       </c>
     </row>
     <row r="432" spans="2:13" x14ac:dyDescent="0.25">
@@ -52996,7 +52996,7 @@
         <v>33</v>
       </c>
       <c r="M432">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016432</v>
       </c>
     </row>
     <row r="433" spans="2:13" x14ac:dyDescent="0.25">
@@ -53025,7 +53025,7 @@
         <v>33</v>
       </c>
       <c r="M433">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016432</v>
       </c>
     </row>
     <row r="434" spans="2:13" x14ac:dyDescent="0.25">
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22B0FF71-450F-4164-841D-1C53E6C88954}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132D2320-6F23-4B93-96FB-0674D4A75415}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4DA6B0E-9CEA-4C0C-B5A3-D0065D32E049}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3852BBDF-CDE2-4313-BD10-50310E894AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{1A497B3C-2D05-41F7-91CE-D66BB5CD0832}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{12F77208-2615-4E98-8E22-3ADE7F79C73B}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B51791-16B5-4842-AAE2-6863B68BD284}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3A4C99-9E73-4861-A62F-1E222ADB968F}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5651E21-F22A-4A71-B603-C8F5842A0D36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C7A9BF-30B1-486F-BE40-0945C821FAEA}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C057A573-EB7B-4D36-870A-949B51E5E205}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBA9FE5-AEC5-44F4-B137-C1501A89D37C}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE4FF06-0E54-4F26-8608-8D83DBEB9C30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{483A0B7F-4022-4A6A-98A9-7D8FA407F1DB}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35401,7 +35401,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S114" t="s">
         <v>500</v>
@@ -35460,7 +35460,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S115" t="s">
         <v>500</v>
@@ -36463,7 +36463,7 @@
         <v>14</v>
       </c>
       <c r="R132" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S132" t="s">
         <v>500</v>
@@ -36522,7 +36522,7 @@
         <v>14</v>
       </c>
       <c r="R133" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S133" t="s">
         <v>500</v>
@@ -36581,7 +36581,7 @@
         <v>14</v>
       </c>
       <c r="R134" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S134" t="s">
         <v>500</v>
@@ -36640,7 +36640,7 @@
         <v>14</v>
       </c>
       <c r="R135" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S135" t="s">
         <v>500</v>
@@ -38029,10 +38029,10 @@
         <v>2024</v>
       </c>
       <c r="G159">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H159">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I159">
         <v>1610</v>
@@ -38088,10 +38088,10 @@
         <v>2024</v>
       </c>
       <c r="G160">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="H160">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="I160">
         <v>1610</v>
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{132D2320-6F23-4B93-96FB-0674D4A75415}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717C3743-8E61-44EA-9EF8-258F9AC48078}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3852BBDF-CDE2-4313-BD10-50310E894AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D72A3D81-CD58-4A72-9568-A74463509B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{12F77208-2615-4E98-8E22-3ADE7F79C73B}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{F1DD52E2-58CD-487D-9D07-53947B2781F0}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF3A4C99-9E73-4861-A62F-1E222ADB968F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C51851C-199D-4342-8219-ACAD94D232F5}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C7A9BF-30B1-486F-BE40-0945C821FAEA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DEBBBAB-6D35-462D-A1A7-D3A27C67B245}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -12710,7 +12710,7 @@
         <v>14</v>
       </c>
       <c r="R128" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S128" t="s">
         <v>500</v>
@@ -12772,7 +12772,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S129" t="s">
         <v>500</v>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBBA9FE5-AEC5-44F4-B137-C1501A89D37C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA2DE28-D832-4423-AD64-2DEB2FA4DD2D}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{483A0B7F-4022-4A6A-98A9-7D8FA407F1DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6BDD1D-B4A4-489B-8E83-439D5E556711}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -36227,7 +36227,7 @@
         <v>14</v>
       </c>
       <c r="R128" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S128" t="s">
         <v>500</v>
@@ -36286,7 +36286,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S129" t="s">
         <v>500</v>
@@ -36463,7 +36463,7 @@
         <v>14</v>
       </c>
       <c r="R132" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S132" t="s">
         <v>500</v>
@@ -36522,7 +36522,7 @@
         <v>14</v>
       </c>
       <c r="R133" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S133" t="s">
         <v>500</v>
@@ -36581,7 +36581,7 @@
         <v>14</v>
       </c>
       <c r="R134" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S134" t="s">
         <v>500</v>
@@ -36640,7 +36640,7 @@
         <v>14</v>
       </c>
       <c r="R135" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S135" t="s">
         <v>500</v>
@@ -36699,7 +36699,7 @@
         <v>14</v>
       </c>
       <c r="R136" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S136" t="s">
         <v>500</v>
@@ -36758,7 +36758,7 @@
         <v>14</v>
       </c>
       <c r="R137" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S137" t="s">
         <v>500</v>
@@ -51168,7 +51168,7 @@
         <v>14</v>
       </c>
       <c r="R382" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S382" t="s">
         <v>500</v>
@@ -51227,7 +51227,7 @@
         <v>14</v>
       </c>
       <c r="R383" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S383" t="s">
         <v>500</v>
@@ -52967,7 +52967,7 @@
         <v>33</v>
       </c>
       <c r="M431">
-        <v>0.19280418494016432</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="432" spans="2:13" x14ac:dyDescent="0.25">
@@ -52996,7 +52996,7 @@
         <v>33</v>
       </c>
       <c r="M432">
-        <v>0.19280418494016432</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="433" spans="2:13" x14ac:dyDescent="0.25">
@@ -53025,7 +53025,7 @@
         <v>33</v>
       </c>
       <c r="M433">
-        <v>0.19280418494016432</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="434" spans="2:13" x14ac:dyDescent="0.25">
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{717C3743-8E61-44EA-9EF8-258F9AC48078}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED0649F-2351-48F5-850E-E3596512D9D7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D72A3D81-CD58-4A72-9568-A74463509B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDBDBDF9-3074-4CC9-9C69-6247269511F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{F1DD52E2-58CD-487D-9D07-53947B2781F0}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{1463146B-5342-46CA-81C7-C3209BC9E841}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C51851C-199D-4342-8219-ACAD94D232F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E713B84-1331-46F9-A94B-E73455F12AAD}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DEBBBAB-6D35-462D-A1A7-D3A27C67B245}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CCD4C04-1361-4A14-B5E9-6C8307E5C6EF}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -12586,7 +12586,7 @@
         <v>14</v>
       </c>
       <c r="R126" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S126" t="s">
         <v>500</v>
@@ -12648,7 +12648,7 @@
         <v>14</v>
       </c>
       <c r="R127" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S127" t="s">
         <v>500</v>
@@ -12834,7 +12834,7 @@
         <v>14</v>
       </c>
       <c r="R130" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S130" t="s">
         <v>500</v>
@@ -12896,7 +12896,7 @@
         <v>14</v>
       </c>
       <c r="R131" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S131" t="s">
         <v>500</v>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA2DE28-D832-4423-AD64-2DEB2FA4DD2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF76A7CA-025D-4F7A-903D-B7A840568C80}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F6BDD1D-B4A4-489B-8E83-439D5E556711}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB3F3F6-8FE5-4876-B32E-F72C08C7953C}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35401,7 +35401,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S114" t="s">
         <v>500</v>
@@ -35460,7 +35460,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S115" t="s">
         <v>500</v>
@@ -36227,7 +36227,7 @@
         <v>14</v>
       </c>
       <c r="R128" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S128" t="s">
         <v>500</v>
@@ -36286,7 +36286,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S129" t="s">
         <v>500</v>
@@ -38029,10 +38029,10 @@
         <v>2024</v>
       </c>
       <c r="G159">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="H159">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="I159">
         <v>1610</v>
@@ -38088,10 +38088,10 @@
         <v>2024</v>
       </c>
       <c r="G160">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H160">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I160">
         <v>1610</v>
@@ -38976,16 +38976,16 @@
         <v>0.1</v>
       </c>
       <c r="H175">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="I175">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="J175">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="K175">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="L175">
         <v>50</v>
@@ -39035,16 +39035,16 @@
         <v>0.1</v>
       </c>
       <c r="H176">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I176">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="J176">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="K176">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L176">
         <v>50</v>
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ED0649F-2351-48F5-850E-E3596512D9D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE7F32A-E5AC-48CD-A3A8-08E672C4F9A8}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDBDBDF9-3074-4CC9-9C69-6247269511F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E34DB3E-449F-49DB-9D49-60A6D71AAEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{1463146B-5342-46CA-81C7-C3209BC9E841}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{E1EF6FA3-28B6-4CC5-B693-256886161B9C}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E713B84-1331-46F9-A94B-E73455F12AAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6158A269-D1D4-4CA1-B414-D7FC654FB061}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CCD4C04-1361-4A14-B5E9-6C8307E5C6EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4D6CD0-7A51-4138-8316-0ADD8F4319BF}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11470,7 +11470,7 @@
         <v>14</v>
       </c>
       <c r="R108" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S108" t="s">
         <v>500</v>
@@ -11532,7 +11532,7 @@
         <v>14</v>
       </c>
       <c r="R109" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S109" t="s">
         <v>500</v>
@@ -12338,7 +12338,7 @@
         <v>14</v>
       </c>
       <c r="R122" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S122" t="s">
         <v>500</v>
@@ -12400,7 +12400,7 @@
         <v>14</v>
       </c>
       <c r="R123" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S123" t="s">
         <v>500</v>
@@ -12710,7 +12710,7 @@
         <v>14</v>
       </c>
       <c r="R128" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S128" t="s">
         <v>500</v>
@@ -12772,7 +12772,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S129" t="s">
         <v>500</v>
@@ -12834,7 +12834,7 @@
         <v>14</v>
       </c>
       <c r="R130" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S130" t="s">
         <v>500</v>
@@ -12896,7 +12896,7 @@
         <v>14</v>
       </c>
       <c r="R131" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S131" t="s">
         <v>500</v>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF76A7CA-025D-4F7A-903D-B7A840568C80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5178A1A-B6D0-417B-A7BD-3AF5BC5B8861}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB3F3F6-8FE5-4876-B32E-F72C08C7953C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D4868E-694D-429E-8FC3-A86D32D2AD64}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35401,7 +35401,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S114" t="s">
         <v>500</v>
@@ -35460,7 +35460,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S115" t="s">
         <v>500</v>
@@ -36463,7 +36463,7 @@
         <v>14</v>
       </c>
       <c r="R132" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S132" t="s">
         <v>500</v>
@@ -36522,7 +36522,7 @@
         <v>14</v>
       </c>
       <c r="R133" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S133" t="s">
         <v>500</v>
@@ -36581,7 +36581,7 @@
         <v>14</v>
       </c>
       <c r="R134" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S134" t="s">
         <v>500</v>
@@ -36640,7 +36640,7 @@
         <v>14</v>
       </c>
       <c r="R135" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S135" t="s">
         <v>500</v>
@@ -38029,10 +38029,10 @@
         <v>2024</v>
       </c>
       <c r="G159">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H159">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I159">
         <v>1610</v>
@@ -38088,10 +38088,10 @@
         <v>2024</v>
       </c>
       <c r="G160">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="H160">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="I160">
         <v>1610</v>
@@ -38976,16 +38976,16 @@
         <v>0.1</v>
       </c>
       <c r="H175">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I175">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="J175">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="K175">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L175">
         <v>50</v>
@@ -39035,16 +39035,16 @@
         <v>0.1</v>
       </c>
       <c r="H176">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="I176">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="J176">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="K176">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="L176">
         <v>50</v>
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE7F32A-E5AC-48CD-A3A8-08E672C4F9A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087D4DC4-8F39-40B2-B6B2-A86ADCE92E88}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E34DB3E-449F-49DB-9D49-60A6D71AAEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AD807F7-8ABC-46AC-A087-88E82EF13AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" xr2:uid="{E1EF6FA3-28B6-4CC5-B693-256886161B9C}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{4C823041-4D00-4732-9E7B-4F5B25384051}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6158A269-D1D4-4CA1-B414-D7FC654FB061}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731802A3-E629-4D7D-8D6A-198605805BAC}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F4D6CD0-7A51-4138-8316-0ADD8F4319BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D59F7B-123E-4BAB-9D6C-2F006BE58D43}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -12586,7 +12586,7 @@
         <v>14</v>
       </c>
       <c r="R126" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S126" t="s">
         <v>500</v>
@@ -12648,7 +12648,7 @@
         <v>14</v>
       </c>
       <c r="R127" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S127" t="s">
         <v>500</v>
@@ -12710,7 +12710,7 @@
         <v>14</v>
       </c>
       <c r="R128" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S128" t="s">
         <v>500</v>
@@ -12772,7 +12772,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S129" t="s">
         <v>500</v>
@@ -12834,7 +12834,7 @@
         <v>14</v>
       </c>
       <c r="R130" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S130" t="s">
         <v>500</v>
@@ -12896,7 +12896,7 @@
         <v>14</v>
       </c>
       <c r="R131" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S131" t="s">
         <v>500</v>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5178A1A-B6D0-417B-A7BD-3AF5BC5B8861}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD96708-E7F7-4463-A4AC-6D009E7E902F}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69D4868E-694D-429E-8FC3-A86D32D2AD64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7DC96EA-9638-4440-A6CA-2CB09EAD883B}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -35401,7 +35401,7 @@
         <v>14</v>
       </c>
       <c r="R114" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S114" t="s">
         <v>500</v>
@@ -35460,7 +35460,7 @@
         <v>14</v>
       </c>
       <c r="R115" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S115" t="s">
         <v>500</v>
@@ -36227,7 +36227,7 @@
         <v>14</v>
       </c>
       <c r="R128" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S128" t="s">
         <v>500</v>
@@ -36286,7 +36286,7 @@
         <v>14</v>
       </c>
       <c r="R129" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S129" t="s">
         <v>500</v>
@@ -36581,7 +36581,7 @@
         <v>14</v>
       </c>
       <c r="R134" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S134" t="s">
         <v>500</v>
@@ -36640,7 +36640,7 @@
         <v>14</v>
       </c>
       <c r="R135" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S135" t="s">
         <v>500</v>
@@ -36699,7 +36699,7 @@
         <v>14</v>
       </c>
       <c r="R136" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S136" t="s">
         <v>500</v>
@@ -36758,7 +36758,7 @@
         <v>14</v>
       </c>
       <c r="R137" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S137" t="s">
         <v>500</v>
@@ -38029,10 +38029,10 @@
         <v>2024</v>
       </c>
       <c r="G159">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="H159">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="I159">
         <v>1610</v>
@@ -38088,10 +38088,10 @@
         <v>2024</v>
       </c>
       <c r="G160">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H160">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I160">
         <v>1610</v>
@@ -38976,16 +38976,16 @@
         <v>0.1</v>
       </c>
       <c r="H175">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="I175">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="J175">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="K175">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="L175">
         <v>50</v>
@@ -39035,16 +39035,16 @@
         <v>0.1</v>
       </c>
       <c r="H176">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I176">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="J176">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="K176">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L176">
         <v>50</v>
@@ -52967,7 +52967,7 @@
         <v>33</v>
       </c>
       <c r="M431">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016441</v>
       </c>
     </row>
     <row r="432" spans="2:13" x14ac:dyDescent="0.25">
@@ -52996,7 +52996,7 @@
         <v>33</v>
       </c>
       <c r="M432">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016441</v>
       </c>
     </row>
     <row r="433" spans="2:13" x14ac:dyDescent="0.25">
@@ -53025,7 +53025,7 @@
         <v>33</v>
       </c>
       <c r="M433">
-        <v>0.19280418494016438</v>
+        <v>0.19280418494016441</v>
       </c>
     </row>
     <row r="434" spans="2:13" x14ac:dyDescent="0.25">
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087D4DC4-8F39-40B2-B6B2-A86ADCE92E88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A3E114-8ACC-46A9-8D41-CEFCDCAAEB67}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2AD807F7-8ABC-46AC-A087-88E82EF13AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB34A5A1-2ECF-46DF-A3B7-91725FB8BF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{4C823041-4D00-4732-9E7B-4F5B25384051}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{0AFCAD99-DA24-4E31-A3BF-EF76A07C10D8}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{731802A3-E629-4D7D-8D6A-198605805BAC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCA7F38-0AB9-4275-A5E1-4924C8EE732F}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D59F7B-123E-4BAB-9D6C-2F006BE58D43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280127FF-5AE2-455B-8BF8-519612F34320}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11470,7 +11470,7 @@
         <v>14</v>
       </c>
       <c r="R108" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S108" t="s">
         <v>500</v>
@@ -11532,7 +11532,7 @@
         <v>14</v>
       </c>
       <c r="R109" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S109" t="s">
         <v>500</v>
@@ -12586,7 +12586,7 @@
         <v>14</v>
       </c>
       <c r="R126" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S126" t="s">
         <v>500</v>
@@ -12648,7 +12648,7 @@
         <v>14</v>
       </c>
       <c r="R127" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S127" t="s">
         <v>500</v>
@@ -12834,7 +12834,7 @@
         <v>14</v>
       </c>
       <c r="R130" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S130" t="s">
         <v>500</v>
@@ -12896,7 +12896,7 @@
         <v>14</v>
       </c>
       <c r="R131" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S131" t="s">
         <v>500</v>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCD96708-E7F7-4463-A4AC-6D009E7E902F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F624C23A-B2A2-489F-B956-8F0146DFD76F}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7DC96EA-9638-4440-A6CA-2CB09EAD883B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E044355-B59F-4517-9641-CF3A6D90AFA4}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -36463,7 +36463,7 @@
         <v>14</v>
       </c>
       <c r="R132" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S132" t="s">
         <v>500</v>
@@ -36522,7 +36522,7 @@
         <v>14</v>
       </c>
       <c r="R133" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S133" t="s">
         <v>500</v>
@@ -36699,7 +36699,7 @@
         <v>14</v>
       </c>
       <c r="R136" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S136" t="s">
         <v>500</v>
@@ -36758,7 +36758,7 @@
         <v>14</v>
       </c>
       <c r="R137" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S137" t="s">
         <v>500</v>
@@ -38029,10 +38029,10 @@
         <v>2024</v>
       </c>
       <c r="G159">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H159">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I159">
         <v>1610</v>
@@ -38088,10 +38088,10 @@
         <v>2024</v>
       </c>
       <c r="G160">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="H160">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="I160">
         <v>1610</v>
@@ -51168,7 +51168,7 @@
         <v>14</v>
       </c>
       <c r="R382" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S382" t="s">
         <v>500</v>
@@ -51227,7 +51227,7 @@
         <v>14</v>
       </c>
       <c r="R383" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S383" t="s">
         <v>500</v>
@@ -52967,7 +52967,7 @@
         <v>33</v>
       </c>
       <c r="M431">
-        <v>0.19280418494016441</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="432" spans="2:13" x14ac:dyDescent="0.25">
@@ -52996,7 +52996,7 @@
         <v>33</v>
       </c>
       <c r="M432">
-        <v>0.19280418494016441</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="433" spans="2:13" x14ac:dyDescent="0.25">
@@ -53025,7 +53025,7 @@
         <v>33</v>
       </c>
       <c r="M433">
-        <v>0.19280418494016441</v>
+        <v>0.19280418494016438</v>
       </c>
     </row>
     <row r="434" spans="2:13" x14ac:dyDescent="0.25">
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A3E114-8ACC-46A9-8D41-CEFCDCAAEB67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D30AEB-8D74-48F7-AE97-A6E76B423B54}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
+++ b/VerveStacks_IDN_grids_kan/vt_vervestacks_IDN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB34A5A1-2ECF-46DF-A3B7-91725FB8BF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{596B694E-5EDC-4921-B54C-0E62FFBE2B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" xr2:uid="{0AFCAD99-DA24-4E31-A3BF-EF76A07C10D8}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{AA6A6E8F-00F5-404D-82E6-77FE27ED2FED}"/>
   </bookViews>
   <sheets>
     <sheet name="additional_hydro_pot" sheetId="5" r:id="rId1"/>
@@ -5030,7 +5030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BCA7F38-0AB9-4275-A5E1-4924C8EE732F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3263B55-4B3D-46C8-AD77-F13BBD24DCD0}">
   <dimension ref="B9:O16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -5335,7 +5335,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280127FF-5AE2-455B-8BF8-519612F34320}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAF9ADC3-55BB-40CE-AE47-5B8BF7A116D9}">
   <dimension ref="B9:V257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -12338,7 +12338,7 @@
         <v>14</v>
       </c>
       <c r="R122" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="S122" t="s">
         <v>500</v>
@@ -12400,7 +12400,7 @@
         <v>14</v>
       </c>
       <c r="R123" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="S123" t="s">
         <v>500</v>
@@ -20549,7 +20549,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F624C23A-B2A2-489F-B956-8F0146DFD76F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE5B1BF-27DD-4F97-9A34-9EDA0CE9EC7E}">
   <dimension ref="B9:V154"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -29206,7 +29206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E044355-B59F-4517-9641-CF3A6D90AFA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB0BCA02-592A-4C5A-9344-FFFC857DAEA2}">
   <dimension ref="B9:V455"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -36699,7 +36699,7 @@
         <v>14</v>
       </c>
       <c r="R136" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S136" t="s">
         <v>500</v>
@@ -36758,7 +36758,7 @@
         <v>14</v>
       </c>
       <c r="R137" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S137" t="s">
         <v>500</v>
@@ -38029,10 +38029,10 @@
         <v>2024</v>
       </c>
       <c r="G159">
-        <v>0.11700000000000001</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="H159">
-        <v>0.32640000000000002</v>
+        <v>0.32639999999999997</v>
       </c>
       <c r="I159">
         <v>1610</v>
@@ -38088,10 +38088,10 @@
         <v>2024</v>
       </c>
       <c r="G160">
-        <v>0.23300000000000001</v>
+        <v>0.11700000000000001</v>
       </c>
       <c r="H160">
-        <v>0.32639999999999997</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I160">
         <v>1610</v>
@@ -38976,16 +38976,16 @@
         <v>0.1</v>
       </c>
       <c r="H175">
-        <v>0.31680000000000003</v>
+        <v>0.32640000000000002</v>
       </c>
       <c r="I175">
-        <v>1889.9999999999998</v>
+        <v>1610</v>
       </c>
       <c r="J175">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="K175">
-        <v>4.8000000000000007</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="L175">
         <v>50</v>
@@ -39035,16 +39035,16 @@
         <v>0.1</v>
       </c>
       <c r="H176">
-        <v>0.32640000000000002</v>
+        <v>0.31680000000000003</v>
       </c>
       <c r="I176">
-        <v>1610</v>
+        <v>1889.9999999999998</v>
       </c>
       <c r="J176">
-        <v>49.5</v>
+        <v>58.5</v>
       </c>
       <c r="K176">
-        <v>4.4000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="L176">
         <v>50</v>
@@ -51168,7 +51168,7 @@
         <v>14</v>
       </c>
       <c r="R382" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="S382" t="s">
         <v>500</v>
@@ -51227,7 +51227,7 @@
         <v>14</v>
       </c>
       <c r="R383" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="S383" t="s">
         <v>500</v>
@@ -53870,7 +53870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D30AEB-8D74-48F7-AE97-A6E76B423B54}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C9EBC7-BC51-468E-8376-1A46A14473D7}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
